--- a/data/tags/סינגלים חדשים זמרים מתחילים/global/2026-02-week01/titles.xlsx
+++ b/data/tags/סינגלים חדשים זמרים מתחילים/global/2026-02-week01/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L7"/>
+  <dimension ref="A1:L8"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>מאיר בן הרוש - קח אוויר קאבר</v>
+        <v>נועה שירי - אבא גדול קאבר</v>
       </c>
       <c r="B2" t="str">
         <v>2026-02-03</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409466&amp;sid=f414d17277694758434992880ac90efb</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409473&amp;sid=4e1c51971e487bd5fef264024f5e19d7</v>
       </c>
       <c r="D2" t="str">
         <v>2026-02-03</v>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>מאיר בן הרוש - קח אוויר קאבר</v>
+        <v>נועה שירי - אבא גדול קאבר</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>הנסיך מהמזרח - הבוגדת קאבר</v>
+        <v>רון אהרוני - מאוהב בגשם קאבר</v>
       </c>
       <c r="B3" t="str">
         <v>2026-02-03</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409465&amp;sid=f414d17277694758434992880ac90efb</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409472&amp;sid=4e1c51971e487bd5fef264024f5e19d7</v>
       </c>
       <c r="D3" t="str">
         <v>2026-02-03</v>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>הנסיך מהמזרח - הבוגדת קאבר</v>
+        <v>רון אהרוני - מאוהב בגשם קאבר</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>בן גורן - האישה הכי יפה בעולם קאבר</v>
+        <v>קורל אמויאל - אמא קאבר</v>
       </c>
       <c r="B4" t="str">
         <v>2026-02-03</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409464&amp;sid=f414d17277694758434992880ac90efb</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409471&amp;sid=4e1c51971e487bd5fef264024f5e19d7</v>
       </c>
       <c r="D4" t="str">
         <v>2026-02-03</v>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>בן גורן - האישה הכי יפה בעולם קאבר</v>
+        <v>קורל אמויאל - אמא קאבר</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>אלרום יעקב - אני ואת קאבר</v>
+        <v>קובי צור - המחר קאבר</v>
       </c>
       <c r="B5" t="str">
         <v>2026-02-03</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409463&amp;sid=f414d17277694758434992880ac90efb</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409470&amp;sid=4e1c51971e487bd5fef264024f5e19d7</v>
       </c>
       <c r="D5" t="str">
         <v>2026-02-03</v>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>אלרום יעקב - אני ואת קאבר</v>
+        <v>קובי צור - המחר קאבר</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>אלמוג טויטו - עת דודים כלה קאבר</v>
+        <v>עקיבא בן חמו - ילדי קאבר</v>
       </c>
       <c r="B6" t="str">
         <v>2026-02-03</v>
       </c>
       <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409462&amp;sid=f414d17277694758434992880ac90efb</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409469&amp;sid=4e1c51971e487bd5fef264024f5e19d7</v>
       </c>
       <c r="D6" t="str">
         <v>2026-02-03</v>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>אלמוג טויטו - עת דודים כלה קאבר</v>
+        <v>עקיבא בן חמו - ילדי קאבר</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>אבישי עוזיאל - השנה החדשה שלי קאבר</v>
+        <v>סהר לוי - גן עדן קאבר</v>
       </c>
       <c r="B7" t="str">
         <v>2026-02-03</v>
       </c>
       <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409461&amp;sid=f414d17277694758434992880ac90efb</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409468&amp;sid=4e1c51971e487bd5fef264024f5e19d7</v>
       </c>
       <c r="D7" t="str">
         <v>2026-02-03</v>
@@ -659,12 +659,50 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>אבישי עוזיאל - השנה החדשה שלי קאבר</v>
+        <v>סהר לוי - גן עדן קאבר</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>נועם צ'נרו - שקט קאבר</v>
+      </c>
+      <c r="B8" t="str">
+        <v>2026-02-03</v>
+      </c>
+      <c r="C8" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409467&amp;sid=4e1c51971e487bd5fef264024f5e19d7</v>
+      </c>
+      <c r="D8" t="str">
+        <v>2026-02-03</v>
+      </c>
+      <c r="E8" t="str">
+        <v/>
+      </c>
+      <c r="F8" t="str">
+        <v/>
+      </c>
+      <c r="G8" t="str">
+        <v/>
+      </c>
+      <c r="H8" t="str">
+        <v/>
+      </c>
+      <c r="I8" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J8" t="str">
+        <v/>
+      </c>
+      <c r="K8" t="str">
+        <v/>
+      </c>
+      <c r="L8" t="str">
+        <v>נועם צ'נרו - שקט קאבר</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L7"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L8"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים זמרים מתחילים/global/2026-02-week01/titles.xlsx
+++ b/data/tags/סינגלים חדשים זמרים מתחילים/global/2026-02-week01/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L8"/>
+  <dimension ref="A1:L3"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>נועה שירי - אבא גדול קאבר</v>
+        <v>ירין אדרי - צעקות וקללות קאבר</v>
       </c>
       <c r="B2" t="str">
         <v>2026-02-03</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409473&amp;sid=4e1c51971e487bd5fef264024f5e19d7</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409475&amp;sid=4b56836c7eac04b8a5fd243ae51039de</v>
       </c>
       <c r="D2" t="str">
         <v>2026-02-03</v>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>נועה שירי - אבא גדול קאבר</v>
+        <v>ירין אדרי - צעקות וקללות קאבר</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>רון אהרוני - מאוהב בגשם קאבר</v>
+        <v>יגאל עדי - מחרוזת נשמה טובה 2026 קאבר</v>
       </c>
       <c r="B3" t="str">
         <v>2026-02-03</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409472&amp;sid=4e1c51971e487bd5fef264024f5e19d7</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409474&amp;sid=4b56836c7eac04b8a5fd243ae51039de</v>
       </c>
       <c r="D3" t="str">
         <v>2026-02-03</v>
@@ -507,202 +507,12 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>רון אהרוני - מאוהב בגשם קאבר</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>קורל אמויאל - אמא קאבר</v>
-      </c>
-      <c r="B4" t="str">
-        <v>2026-02-03</v>
-      </c>
-      <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409471&amp;sid=4e1c51971e487bd5fef264024f5e19d7</v>
-      </c>
-      <c r="D4" t="str">
-        <v>2026-02-03</v>
-      </c>
-      <c r="E4" t="str">
-        <v/>
-      </c>
-      <c r="F4" t="str">
-        <v/>
-      </c>
-      <c r="G4" t="str">
-        <v/>
-      </c>
-      <c r="H4" t="str">
-        <v/>
-      </c>
-      <c r="I4" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
-      </c>
-      <c r="J4" t="str">
-        <v/>
-      </c>
-      <c r="K4" t="str">
-        <v/>
-      </c>
-      <c r="L4" t="str">
-        <v>קורל אמויאל - אמא קאבר</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>קובי צור - המחר קאבר</v>
-      </c>
-      <c r="B5" t="str">
-        <v>2026-02-03</v>
-      </c>
-      <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409470&amp;sid=4e1c51971e487bd5fef264024f5e19d7</v>
-      </c>
-      <c r="D5" t="str">
-        <v>2026-02-03</v>
-      </c>
-      <c r="E5" t="str">
-        <v/>
-      </c>
-      <c r="F5" t="str">
-        <v/>
-      </c>
-      <c r="G5" t="str">
-        <v/>
-      </c>
-      <c r="H5" t="str">
-        <v/>
-      </c>
-      <c r="I5" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
-      </c>
-      <c r="J5" t="str">
-        <v/>
-      </c>
-      <c r="K5" t="str">
-        <v/>
-      </c>
-      <c r="L5" t="str">
-        <v>קובי צור - המחר קאבר</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>עקיבא בן חמו - ילדי קאבר</v>
-      </c>
-      <c r="B6" t="str">
-        <v>2026-02-03</v>
-      </c>
-      <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409469&amp;sid=4e1c51971e487bd5fef264024f5e19d7</v>
-      </c>
-      <c r="D6" t="str">
-        <v>2026-02-03</v>
-      </c>
-      <c r="E6" t="str">
-        <v/>
-      </c>
-      <c r="F6" t="str">
-        <v/>
-      </c>
-      <c r="G6" t="str">
-        <v/>
-      </c>
-      <c r="H6" t="str">
-        <v/>
-      </c>
-      <c r="I6" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
-      </c>
-      <c r="J6" t="str">
-        <v/>
-      </c>
-      <c r="K6" t="str">
-        <v/>
-      </c>
-      <c r="L6" t="str">
-        <v>עקיבא בן חמו - ילדי קאבר</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>סהר לוי - גן עדן קאבר</v>
-      </c>
-      <c r="B7" t="str">
-        <v>2026-02-03</v>
-      </c>
-      <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409468&amp;sid=4e1c51971e487bd5fef264024f5e19d7</v>
-      </c>
-      <c r="D7" t="str">
-        <v>2026-02-03</v>
-      </c>
-      <c r="E7" t="str">
-        <v/>
-      </c>
-      <c r="F7" t="str">
-        <v/>
-      </c>
-      <c r="G7" t="str">
-        <v/>
-      </c>
-      <c r="H7" t="str">
-        <v/>
-      </c>
-      <c r="I7" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
-      </c>
-      <c r="J7" t="str">
-        <v/>
-      </c>
-      <c r="K7" t="str">
-        <v/>
-      </c>
-      <c r="L7" t="str">
-        <v>סהר לוי - גן עדן קאבר</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>נועם צ'נרו - שקט קאבר</v>
-      </c>
-      <c r="B8" t="str">
-        <v>2026-02-03</v>
-      </c>
-      <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409467&amp;sid=4e1c51971e487bd5fef264024f5e19d7</v>
-      </c>
-      <c r="D8" t="str">
-        <v>2026-02-03</v>
-      </c>
-      <c r="E8" t="str">
-        <v/>
-      </c>
-      <c r="F8" t="str">
-        <v/>
-      </c>
-      <c r="G8" t="str">
-        <v/>
-      </c>
-      <c r="H8" t="str">
-        <v/>
-      </c>
-      <c r="I8" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
-      </c>
-      <c r="J8" t="str">
-        <v/>
-      </c>
-      <c r="K8" t="str">
-        <v/>
-      </c>
-      <c r="L8" t="str">
-        <v>נועם צ'נרו - שקט קאבר</v>
+        <v>יגאל עדי - מחרוזת נשמה טובה 2026 קאבר</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L8"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L3"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים זמרים מתחילים/global/2026-02-week01/titles.xlsx
+++ b/data/tags/סינגלים חדשים זמרים מתחילים/global/2026-02-week01/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L3"/>
+  <dimension ref="A1:L2"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>ירין אדרי - צעקות וקללות קאבר</v>
+        <v>טל בן מויאל - אהבה ברכב קאבר</v>
       </c>
       <c r="B2" t="str">
         <v>2026-02-03</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409475&amp;sid=4b56836c7eac04b8a5fd243ae51039de</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409476&amp;sid=85a43ebc12c9917d756b212c36ac93e5</v>
       </c>
       <c r="D2" t="str">
         <v>2026-02-03</v>
@@ -469,50 +469,12 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>ירין אדרי - צעקות וקללות קאבר</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>יגאל עדי - מחרוזת נשמה טובה 2026 קאבר</v>
-      </c>
-      <c r="B3" t="str">
-        <v>2026-02-03</v>
-      </c>
-      <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409474&amp;sid=4b56836c7eac04b8a5fd243ae51039de</v>
-      </c>
-      <c r="D3" t="str">
-        <v>2026-02-03</v>
-      </c>
-      <c r="E3" t="str">
-        <v/>
-      </c>
-      <c r="F3" t="str">
-        <v/>
-      </c>
-      <c r="G3" t="str">
-        <v/>
-      </c>
-      <c r="H3" t="str">
-        <v/>
-      </c>
-      <c r="I3" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
-      </c>
-      <c r="J3" t="str">
-        <v/>
-      </c>
-      <c r="K3" t="str">
-        <v/>
-      </c>
-      <c r="L3" t="str">
-        <v>יגאל עדי - מחרוזת נשמה טובה 2026 קאבר</v>
+        <v>טל בן מויאל - אהבה ברכב קאבר</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים זמרים מתחילים/global/2026-02-week01/titles.xlsx
+++ b/data/tags/סינגלים חדשים זמרים מתחילים/global/2026-02-week01/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:L10"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,16 +436,16 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>טל בן מויאל - אהבה ברכב קאבר</v>
+        <v>רויטל ממן - פנים מול פנים קאבר</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-02-03</v>
+        <v>2026-02-06</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409476&amp;sid=85a43ebc12c9917d756b212c36ac93e5</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409522&amp;sid=f0e00bbc4d1bddf9c89a3594b637bfab</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-02-03</v>
+        <v>2026-02-06</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -469,12 +469,316 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>טל בן מויאל - אהבה ברכב קאבר</v>
+        <v>רויטל ממן - פנים מול פנים קאבר</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>נתנאל ברק - הספסל השבור קאבר</v>
+      </c>
+      <c r="B3" t="str">
+        <v>2026-02-06</v>
+      </c>
+      <c r="C3" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409521&amp;sid=f0e00bbc4d1bddf9c89a3594b637bfab</v>
+      </c>
+      <c r="D3" t="str">
+        <v>2026-02-06</v>
+      </c>
+      <c r="E3" t="str">
+        <v/>
+      </c>
+      <c r="F3" t="str">
+        <v/>
+      </c>
+      <c r="G3" t="str">
+        <v/>
+      </c>
+      <c r="H3" t="str">
+        <v/>
+      </c>
+      <c r="I3" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J3" t="str">
+        <v/>
+      </c>
+      <c r="K3" t="str">
+        <v/>
+      </c>
+      <c r="L3" t="str">
+        <v>נתנאל ברק - הספסל השבור קאבר</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>נועם דדון - סיגל קאבר</v>
+      </c>
+      <c r="B4" t="str">
+        <v>2026-02-06</v>
+      </c>
+      <c r="C4" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409520&amp;sid=f0e00bbc4d1bddf9c89a3594b637bfab</v>
+      </c>
+      <c r="D4" t="str">
+        <v>2026-02-06</v>
+      </c>
+      <c r="E4" t="str">
+        <v/>
+      </c>
+      <c r="F4" t="str">
+        <v/>
+      </c>
+      <c r="G4" t="str">
+        <v/>
+      </c>
+      <c r="H4" t="str">
+        <v/>
+      </c>
+      <c r="I4" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J4" t="str">
+        <v/>
+      </c>
+      <c r="K4" t="str">
+        <v/>
+      </c>
+      <c r="L4" t="str">
+        <v>נועם דדון - סיגל קאבר</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>נויה ערבה - גן עדן קאבר</v>
+      </c>
+      <c r="B5" t="str">
+        <v>2026-02-06</v>
+      </c>
+      <c r="C5" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409519&amp;sid=f0e00bbc4d1bddf9c89a3594b637bfab</v>
+      </c>
+      <c r="D5" t="str">
+        <v>2026-02-06</v>
+      </c>
+      <c r="E5" t="str">
+        <v/>
+      </c>
+      <c r="F5" t="str">
+        <v/>
+      </c>
+      <c r="G5" t="str">
+        <v/>
+      </c>
+      <c r="H5" t="str">
+        <v/>
+      </c>
+      <c r="I5" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J5" t="str">
+        <v/>
+      </c>
+      <c r="K5" t="str">
+        <v/>
+      </c>
+      <c r="L5" t="str">
+        <v>נויה ערבה - גן עדן קאבר</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>מאיר רובין - רחקי מכולם קאבר</v>
+      </c>
+      <c r="B6" t="str">
+        <v>2026-02-06</v>
+      </c>
+      <c r="C6" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409518&amp;sid=f0e00bbc4d1bddf9c89a3594b637bfab</v>
+      </c>
+      <c r="D6" t="str">
+        <v>2026-02-06</v>
+      </c>
+      <c r="E6" t="str">
+        <v/>
+      </c>
+      <c r="F6" t="str">
+        <v/>
+      </c>
+      <c r="G6" t="str">
+        <v/>
+      </c>
+      <c r="H6" t="str">
+        <v/>
+      </c>
+      <c r="I6" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J6" t="str">
+        <v/>
+      </c>
+      <c r="K6" t="str">
+        <v/>
+      </c>
+      <c r="L6" t="str">
+        <v>מאיר רובין - רחקי מכולם קאבר</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>יוסי רזיאל - Dar &amp; Dunya Cover</v>
+      </c>
+      <c r="B7" t="str">
+        <v>2026-02-06</v>
+      </c>
+      <c r="C7" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409517&amp;sid=f0e00bbc4d1bddf9c89a3594b637bfab</v>
+      </c>
+      <c r="D7" t="str">
+        <v>2026-02-06</v>
+      </c>
+      <c r="E7" t="str">
+        <v/>
+      </c>
+      <c r="F7" t="str">
+        <v/>
+      </c>
+      <c r="G7" t="str">
+        <v/>
+      </c>
+      <c r="H7" t="str">
+        <v/>
+      </c>
+      <c r="I7" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J7" t="str">
+        <v/>
+      </c>
+      <c r="K7" t="str">
+        <v/>
+      </c>
+      <c r="L7" t="str">
+        <v>יוסי רזיאל - Dar &amp; Dunya Cover</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>דניאל דרחי - מדאם קאבר</v>
+      </c>
+      <c r="B8" t="str">
+        <v>2026-02-06</v>
+      </c>
+      <c r="C8" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409516&amp;sid=f0e00bbc4d1bddf9c89a3594b637bfab</v>
+      </c>
+      <c r="D8" t="str">
+        <v>2026-02-06</v>
+      </c>
+      <c r="E8" t="str">
+        <v/>
+      </c>
+      <c r="F8" t="str">
+        <v/>
+      </c>
+      <c r="G8" t="str">
+        <v/>
+      </c>
+      <c r="H8" t="str">
+        <v/>
+      </c>
+      <c r="I8" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J8" t="str">
+        <v/>
+      </c>
+      <c r="K8" t="str">
+        <v/>
+      </c>
+      <c r="L8" t="str">
+        <v>דניאל דרחי - מדאם קאבר</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>דור כהן - מקלט לדמעותיי קאבר</v>
+      </c>
+      <c r="B9" t="str">
+        <v>2026-02-06</v>
+      </c>
+      <c r="C9" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409515&amp;sid=f0e00bbc4d1bddf9c89a3594b637bfab</v>
+      </c>
+      <c r="D9" t="str">
+        <v>2026-02-06</v>
+      </c>
+      <c r="E9" t="str">
+        <v/>
+      </c>
+      <c r="F9" t="str">
+        <v/>
+      </c>
+      <c r="G9" t="str">
+        <v/>
+      </c>
+      <c r="H9" t="str">
+        <v/>
+      </c>
+      <c r="I9" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J9" t="str">
+        <v/>
+      </c>
+      <c r="K9" t="str">
+        <v/>
+      </c>
+      <c r="L9" t="str">
+        <v>דור כהן - מקלט לדמעותיי קאבר</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>אודי דמארי - פשוט אנשים קאבר</v>
+      </c>
+      <c r="B10" t="str">
+        <v>2026-02-06</v>
+      </c>
+      <c r="C10" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409514&amp;sid=f0e00bbc4d1bddf9c89a3594b637bfab</v>
+      </c>
+      <c r="D10" t="str">
+        <v>2026-02-06</v>
+      </c>
+      <c r="E10" t="str">
+        <v/>
+      </c>
+      <c r="F10" t="str">
+        <v/>
+      </c>
+      <c r="G10" t="str">
+        <v/>
+      </c>
+      <c r="H10" t="str">
+        <v/>
+      </c>
+      <c r="I10" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J10" t="str">
+        <v/>
+      </c>
+      <c r="K10" t="str">
+        <v/>
+      </c>
+      <c r="L10" t="str">
+        <v>אודי דמארי - פשוט אנשים קאבר</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L10"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים זמרים מתחילים/global/2026-02-week01/titles.xlsx
+++ b/data/tags/סינגלים חדשים זמרים מתחילים/global/2026-02-week01/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L10"/>
+  <dimension ref="A1:L4"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,16 +436,16 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>רויטל ממן - פנים מול פנים קאבר</v>
+        <v>חנוך שובל - אם את כבר הולכת קאבר</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-02-06</v>
+        <v>2026-02-07</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409522&amp;sid=f0e00bbc4d1bddf9c89a3594b637bfab</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409525&amp;sid=9e4903f19460a872420e6f4f858cba90</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-02-06</v>
+        <v>2026-02-07</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -469,21 +469,21 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>רויטל ממן - פנים מול פנים קאבר</v>
+        <v>חנוך שובל - אם את כבר הולכת קאבר</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>נתנאל ברק - הספסל השבור קאבר</v>
+        <v>אליה ביתן - אל תעזוב אותי קאבר</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-02-06</v>
+        <v>2026-02-07</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409521&amp;sid=f0e00bbc4d1bddf9c89a3594b637bfab</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409524&amp;sid=9e4903f19460a872420e6f4f858cba90</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-02-06</v>
+        <v>2026-02-07</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -507,21 +507,21 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>נתנאל ברק - הספסל השבור קאבר</v>
+        <v>אליה ביתן - אל תעזוב אותי קאבר</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>נועם דדון - סיגל קאבר</v>
+        <v>אבישי עוזיאל - יש מבול קאבר</v>
       </c>
       <c r="B4" t="str">
-        <v>2026-02-06</v>
+        <v>2026-02-07</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409520&amp;sid=f0e00bbc4d1bddf9c89a3594b637bfab</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409523&amp;sid=9e4903f19460a872420e6f4f858cba90</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-02-06</v>
+        <v>2026-02-07</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -545,240 +545,12 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>נועם דדון - סיגל קאבר</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>נויה ערבה - גן עדן קאבר</v>
-      </c>
-      <c r="B5" t="str">
-        <v>2026-02-06</v>
-      </c>
-      <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409519&amp;sid=f0e00bbc4d1bddf9c89a3594b637bfab</v>
-      </c>
-      <c r="D5" t="str">
-        <v>2026-02-06</v>
-      </c>
-      <c r="E5" t="str">
-        <v/>
-      </c>
-      <c r="F5" t="str">
-        <v/>
-      </c>
-      <c r="G5" t="str">
-        <v/>
-      </c>
-      <c r="H5" t="str">
-        <v/>
-      </c>
-      <c r="I5" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
-      </c>
-      <c r="J5" t="str">
-        <v/>
-      </c>
-      <c r="K5" t="str">
-        <v/>
-      </c>
-      <c r="L5" t="str">
-        <v>נויה ערבה - גן עדן קאבר</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>מאיר רובין - רחקי מכולם קאבר</v>
-      </c>
-      <c r="B6" t="str">
-        <v>2026-02-06</v>
-      </c>
-      <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409518&amp;sid=f0e00bbc4d1bddf9c89a3594b637bfab</v>
-      </c>
-      <c r="D6" t="str">
-        <v>2026-02-06</v>
-      </c>
-      <c r="E6" t="str">
-        <v/>
-      </c>
-      <c r="F6" t="str">
-        <v/>
-      </c>
-      <c r="G6" t="str">
-        <v/>
-      </c>
-      <c r="H6" t="str">
-        <v/>
-      </c>
-      <c r="I6" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
-      </c>
-      <c r="J6" t="str">
-        <v/>
-      </c>
-      <c r="K6" t="str">
-        <v/>
-      </c>
-      <c r="L6" t="str">
-        <v>מאיר רובין - רחקי מכולם קאבר</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>יוסי רזיאל - Dar &amp; Dunya Cover</v>
-      </c>
-      <c r="B7" t="str">
-        <v>2026-02-06</v>
-      </c>
-      <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409517&amp;sid=f0e00bbc4d1bddf9c89a3594b637bfab</v>
-      </c>
-      <c r="D7" t="str">
-        <v>2026-02-06</v>
-      </c>
-      <c r="E7" t="str">
-        <v/>
-      </c>
-      <c r="F7" t="str">
-        <v/>
-      </c>
-      <c r="G7" t="str">
-        <v/>
-      </c>
-      <c r="H7" t="str">
-        <v/>
-      </c>
-      <c r="I7" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
-      </c>
-      <c r="J7" t="str">
-        <v/>
-      </c>
-      <c r="K7" t="str">
-        <v/>
-      </c>
-      <c r="L7" t="str">
-        <v>יוסי רזיאל - Dar &amp; Dunya Cover</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>דניאל דרחי - מדאם קאבר</v>
-      </c>
-      <c r="B8" t="str">
-        <v>2026-02-06</v>
-      </c>
-      <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409516&amp;sid=f0e00bbc4d1bddf9c89a3594b637bfab</v>
-      </c>
-      <c r="D8" t="str">
-        <v>2026-02-06</v>
-      </c>
-      <c r="E8" t="str">
-        <v/>
-      </c>
-      <c r="F8" t="str">
-        <v/>
-      </c>
-      <c r="G8" t="str">
-        <v/>
-      </c>
-      <c r="H8" t="str">
-        <v/>
-      </c>
-      <c r="I8" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
-      </c>
-      <c r="J8" t="str">
-        <v/>
-      </c>
-      <c r="K8" t="str">
-        <v/>
-      </c>
-      <c r="L8" t="str">
-        <v>דניאל דרחי - מדאם קאבר</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>דור כהן - מקלט לדמעותיי קאבר</v>
-      </c>
-      <c r="B9" t="str">
-        <v>2026-02-06</v>
-      </c>
-      <c r="C9" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409515&amp;sid=f0e00bbc4d1bddf9c89a3594b637bfab</v>
-      </c>
-      <c r="D9" t="str">
-        <v>2026-02-06</v>
-      </c>
-      <c r="E9" t="str">
-        <v/>
-      </c>
-      <c r="F9" t="str">
-        <v/>
-      </c>
-      <c r="G9" t="str">
-        <v/>
-      </c>
-      <c r="H9" t="str">
-        <v/>
-      </c>
-      <c r="I9" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
-      </c>
-      <c r="J9" t="str">
-        <v/>
-      </c>
-      <c r="K9" t="str">
-        <v/>
-      </c>
-      <c r="L9" t="str">
-        <v>דור כהן - מקלט לדמעותיי קאבר</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>אודי דמארי - פשוט אנשים קאבר</v>
-      </c>
-      <c r="B10" t="str">
-        <v>2026-02-06</v>
-      </c>
-      <c r="C10" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=409514&amp;sid=f0e00bbc4d1bddf9c89a3594b637bfab</v>
-      </c>
-      <c r="D10" t="str">
-        <v>2026-02-06</v>
-      </c>
-      <c r="E10" t="str">
-        <v/>
-      </c>
-      <c r="F10" t="str">
-        <v/>
-      </c>
-      <c r="G10" t="str">
-        <v/>
-      </c>
-      <c r="H10" t="str">
-        <v/>
-      </c>
-      <c r="I10" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
-      </c>
-      <c r="J10" t="str">
-        <v/>
-      </c>
-      <c r="K10" t="str">
-        <v/>
-      </c>
-      <c r="L10" t="str">
-        <v>אודי דמארי - פשוט אנשים קאבר</v>
+        <v>אבישי עוזיאל - יש מבול קאבר</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L10"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L4"/>
   </ignoredErrors>
 </worksheet>
 </file>